--- a/Shafi Goth/GBPS Shafi Goth.xlsx
+++ b/Shafi Goth/GBPS Shafi Goth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Shafi Goth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C1AB0C-6DA4-4B05-9DF3-6695B7744EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0392BCAA-B875-45F9-A604-EE0B2D365300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="279">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -873,6 +873,9 @@
   </si>
   <si>
     <t>0317-3269392</t>
+  </si>
+  <si>
+    <t>fayyaz</t>
   </si>
 </sst>
 </file>
@@ -882,7 +885,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -898,11 +901,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -910,7 +920,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -918,7 +928,7 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -926,27 +936,27 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1003,7 +1013,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1065,83 +1075,84 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3176,7 +3187,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AAED2D2-59CD-4BFC-9DE5-6AE9C98460DA}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="20" customWidth="1"/>
@@ -5006,6 +5017,11 @@
       <c r="M43" s="19"/>
       <c r="N43" s="19" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="E45" s="38" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -6644,7 +6660,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="L1:L9 L11:L1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>

--- a/Shafi Goth/GBPS Shafi Goth.xlsx
+++ b/Shafi Goth/GBPS Shafi Goth.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Shafi Goth\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC86232-9DA6-4383-92BF-B840D7970850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE" sheetId="1" r:id="rId1"/>
@@ -19,13 +25,13 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Class-1'!$A$1:$N$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Class-2'!$A$1:$N$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Class-3'!$A$1:$N$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Class-4'!$A$1:$N$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Class-5'!$A$1:$N$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Class-3'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Class-4'!$A$1:$N$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Class-5'!$A$1:$N$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ECE!$A$1:$N$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">KG!$A$1:$N$43</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="596">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -1394,12 +1400,447 @@
   </si>
   <si>
     <t>42201-8065602-5</t>
+  </si>
+  <si>
+    <t>Asadullah</t>
+  </si>
+  <si>
+    <t>Class-3</t>
+  </si>
+  <si>
+    <t>42301-9477690-7</t>
+  </si>
+  <si>
+    <t>Aziz</t>
+  </si>
+  <si>
+    <t>0310-4505670</t>
+  </si>
+  <si>
+    <t>Ahmed Ullah</t>
+  </si>
+  <si>
+    <t>43103-8701328-5</t>
+  </si>
+  <si>
+    <t>Asad Ali</t>
+  </si>
+  <si>
+    <t>Liaqat Ali</t>
+  </si>
+  <si>
+    <t>Abdul Habib</t>
+  </si>
+  <si>
+    <t>Khuda Bukhsh</t>
+  </si>
+  <si>
+    <t>42201-1234681-9</t>
+  </si>
+  <si>
+    <t>Afaq Hussain</t>
+  </si>
+  <si>
+    <t>45204-9282720-1</t>
+  </si>
+  <si>
+    <t>Ali Hasan</t>
+  </si>
+  <si>
+    <t>Zeeshan</t>
+  </si>
+  <si>
+    <t>Shayan</t>
+  </si>
+  <si>
+    <t>Moliyo</t>
+  </si>
+  <si>
+    <t>42501-1598020-5</t>
+  </si>
+  <si>
+    <t>Sher Zaman</t>
+  </si>
+  <si>
+    <t>38302-5427216-5</t>
+  </si>
+  <si>
+    <t>0322-2227524</t>
+  </si>
+  <si>
+    <t>Lachhan</t>
+  </si>
+  <si>
+    <t>Sharmeela</t>
+  </si>
+  <si>
+    <t>Nabeela</t>
+  </si>
+  <si>
+    <t>Shabana Naaz</t>
+  </si>
+  <si>
+    <t>43102-2474505-5</t>
+  </si>
+  <si>
+    <t>Kanwal</t>
+  </si>
+  <si>
+    <t>Nasir Ali</t>
+  </si>
+  <si>
+    <t>Sadia</t>
+  </si>
+  <si>
+    <t>42501-2552662-7</t>
+  </si>
+  <si>
+    <t>Class-5</t>
+  </si>
+  <si>
+    <t>Kamran</t>
+  </si>
+  <si>
+    <t>Bahram</t>
+  </si>
+  <si>
+    <t>42501-3658367-5</t>
+  </si>
+  <si>
+    <t>0300-2732298</t>
+  </si>
+  <si>
+    <t>Zakir Hussain</t>
+  </si>
+  <si>
+    <t>M. Habib</t>
+  </si>
+  <si>
+    <t>Salman Ali</t>
+  </si>
+  <si>
+    <t>Shahid Ali</t>
+  </si>
+  <si>
+    <t>Eshhaq</t>
+  </si>
+  <si>
+    <t>Nazeer Ahmed</t>
+  </si>
+  <si>
+    <t>M. Ismail</t>
+  </si>
+  <si>
+    <t>M. Ikram</t>
+  </si>
+  <si>
+    <t>Ikram Ullah</t>
+  </si>
+  <si>
+    <t>M. Shah Wali</t>
+  </si>
+  <si>
+    <t>Huzaifa</t>
+  </si>
+  <si>
+    <t>Islam Gul</t>
+  </si>
+  <si>
+    <t>Azan</t>
+  </si>
+  <si>
+    <t>Arsalan</t>
+  </si>
+  <si>
+    <t>Ezat Muhammad</t>
+  </si>
+  <si>
+    <t>Mahboob Ali</t>
+  </si>
+  <si>
+    <t>M. Hussain</t>
+  </si>
+  <si>
+    <t>Dua</t>
+  </si>
+  <si>
+    <t>Basheer Ahmed</t>
+  </si>
+  <si>
+    <t>Sabira</t>
+  </si>
+  <si>
+    <t>Aleena</t>
+  </si>
+  <si>
+    <t>Fatima</t>
+  </si>
+  <si>
+    <t>Fghulam Rabbani</t>
+  </si>
+  <si>
+    <t>Marium</t>
+  </si>
+  <si>
+    <t>Shoaib</t>
+  </si>
+  <si>
+    <t>Azra</t>
+  </si>
+  <si>
+    <t>Aijaz Ali</t>
+  </si>
+  <si>
+    <t>Farhana</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>Anum Fatima</t>
+  </si>
+  <si>
+    <t>M. Inam Ul Haq</t>
+  </si>
+  <si>
+    <t>42501-3364689-5</t>
+  </si>
+  <si>
+    <t>42501-3909422-3</t>
+  </si>
+  <si>
+    <t>42501-1433142-5</t>
+  </si>
+  <si>
+    <t>42501-6683151-5</t>
+  </si>
+  <si>
+    <t>21104-6377088-5</t>
+  </si>
+  <si>
+    <t>42401-6325939-7</t>
+  </si>
+  <si>
+    <t>42501-2050546-7</t>
+  </si>
+  <si>
+    <t>42501-1955011-1</t>
+  </si>
+  <si>
+    <t>42101-1506238-3</t>
+  </si>
+  <si>
+    <t>43402-0357514-3</t>
+  </si>
+  <si>
+    <t>42501-7357857-1</t>
+  </si>
+  <si>
+    <t>53201-5807761-0</t>
+  </si>
+  <si>
+    <t>32202-0411580-8</t>
+  </si>
+  <si>
+    <t>0300-2172324</t>
+  </si>
+  <si>
+    <t>0325-8450682</t>
+  </si>
+  <si>
+    <t>0321-2249080</t>
+  </si>
+  <si>
+    <t>0323-2063744</t>
+  </si>
+  <si>
+    <t>0308-7207731</t>
+  </si>
+  <si>
+    <t>0307-2385224</t>
+  </si>
+  <si>
+    <t>0306-2360612</t>
+  </si>
+  <si>
+    <t>0300-2088955</t>
+  </si>
+  <si>
+    <t>0316-2379689</t>
+  </si>
+  <si>
+    <t>0312-8682399</t>
+  </si>
+  <si>
+    <t>0317-7892112</t>
+  </si>
+  <si>
+    <t>0345-2015298</t>
+  </si>
+  <si>
+    <t>0310-2910861</t>
+  </si>
+  <si>
+    <t>0302-3749677</t>
+  </si>
+  <si>
+    <t>Faisal Raza</t>
+  </si>
+  <si>
+    <t>Muhammad Ismail</t>
+  </si>
+  <si>
+    <t>Shakir Hussain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdullah </t>
+  </si>
+  <si>
+    <t>Meer Muhammad</t>
+  </si>
+  <si>
+    <t>42301-1863385-7</t>
+  </si>
+  <si>
+    <t>0345-335583</t>
+  </si>
+  <si>
+    <t>Faizan Ali</t>
+  </si>
+  <si>
+    <t>Hakim Ali</t>
+  </si>
+  <si>
+    <t>Class-4</t>
+  </si>
+  <si>
+    <t>41409-4401364-7</t>
+  </si>
+  <si>
+    <t>0304-3683599</t>
+  </si>
+  <si>
+    <t>Abaish Kumar</t>
+  </si>
+  <si>
+    <t>Pappu Raja</t>
+  </si>
+  <si>
+    <t>53405-3126822-3</t>
+  </si>
+  <si>
+    <t>0300-3703404</t>
+  </si>
+  <si>
+    <t>Aftab</t>
+  </si>
+  <si>
+    <t>Syed Muhammad Shahzain</t>
+  </si>
+  <si>
+    <t>Syed Abdul Razzaq</t>
+  </si>
+  <si>
+    <t>42101-1835327-3</t>
+  </si>
+  <si>
+    <t>0310-0201206</t>
+  </si>
+  <si>
+    <t>Zain ali Magsi</t>
+  </si>
+  <si>
+    <t>Rajab Ali</t>
+  </si>
+  <si>
+    <t>42501-8844989-1</t>
+  </si>
+  <si>
+    <t>0304-9774165</t>
+  </si>
+  <si>
+    <t>Amad Ali</t>
+  </si>
+  <si>
+    <t>Javaid</t>
+  </si>
+  <si>
+    <t>44203-5777250-3</t>
+  </si>
+  <si>
+    <t>0312-2216677</t>
+  </si>
+  <si>
+    <t>Uzair Ali</t>
+  </si>
+  <si>
+    <t>Mazhar Ali</t>
+  </si>
+  <si>
+    <t>42501-5915942-9</t>
+  </si>
+  <si>
+    <t>0341-5940899</t>
+  </si>
+  <si>
+    <t>Tabinda</t>
+  </si>
+  <si>
+    <t>Adnan</t>
+  </si>
+  <si>
+    <t>37301-9735640-3</t>
+  </si>
+  <si>
+    <t>0311-1022408</t>
+  </si>
+  <si>
+    <t>Zubair Ali</t>
+  </si>
+  <si>
+    <t>0324-2139003</t>
+  </si>
+  <si>
+    <t>Mahnoor</t>
+  </si>
+  <si>
+    <t>0302-2595918</t>
+  </si>
+  <si>
+    <t>0302-6062360</t>
+  </si>
+  <si>
+    <t>Aliya</t>
+  </si>
+  <si>
+    <t>Bashir Ahmed</t>
+  </si>
+  <si>
+    <t>43402-0357514-2</t>
+  </si>
+  <si>
+    <t>Bisma</t>
+  </si>
+  <si>
+    <t>Mehek</t>
+  </si>
+  <si>
+    <t>0303-2699260</t>
+  </si>
+  <si>
+    <t>Sidra</t>
+  </si>
+  <si>
+    <t>Afshan Naaz</t>
+  </si>
+  <si>
+    <t>0305-2899249</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
@@ -1666,19 +2107,9 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="29">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="28">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1981,26 +2412,26 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="28"/>
-      <tableStyleElement type="headerRow" dxfId="27"/>
-      <tableStyleElement type="totalRow" dxfId="26"/>
-      <tableStyleElement type="firstColumn" dxfId="25"/>
-      <tableStyleElement type="lastColumn" dxfId="24"/>
-      <tableStyleElement type="firstRowStripe" dxfId="23"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="22"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="27"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="totalRow" dxfId="25"/>
+      <tableStyleElement type="firstColumn" dxfId="24"/>
+      <tableStyleElement type="lastColumn" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="22"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="21"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="totalRow" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="18"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="17"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="16"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="15"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="14"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="13"/>
-      <tableStyleElement type="pageFieldValues" dxfId="12"/>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstRowStripe" dxfId="18"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="16"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="14"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="13"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="12"/>
+      <tableStyleElement type="pageFieldValues" dxfId="11"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2271,7 +2702,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
@@ -3768,7 +4199,7 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -3776,7 +4207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
@@ -5614,7 +6045,7 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -5622,7 +6053,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N51"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
@@ -6794,7 +7225,7 @@
         <v>282</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G28" s="19" t="s">
         <v>229</v>
@@ -7779,10 +8210,10 @@
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="L1:L9 L11:L1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -7790,8 +8221,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N57"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="20" customWidth="1"/>
@@ -9875,123 +10306,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="19">
-        <v>47</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="H49" s="26"/>
-      <c r="I49" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K49" s="26"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="19">
-        <v>48</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="H50" s="26"/>
-      <c r="I50" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K50" s="26"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="19">
-        <v>49</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="25"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="H51" s="26"/>
-      <c r="I51" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K51" s="26"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+    <row r="49" spans="7:7">
+      <c r="G49"/>
+    </row>
+    <row r="50" spans="7:7">
+      <c r="G50"/>
+    </row>
+    <row r="51" spans="7:7">
+      <c r="G51"/>
+    </row>
+    <row r="52" spans="7:7">
       <c r="G52"/>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="7:7">
       <c r="G53"/>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="G54"/>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="G55"/>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="G56"/>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="G57"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="L1:L9 L11:L1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -9999,8 +10337,8 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="20" customWidth="1"/>
@@ -10089,25 +10427,39 @@
       <c r="B3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+      <c r="C3" s="25">
+        <v>1696</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>267</v>
+      </c>
       <c r="F3" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H3" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H3" s="26">
+        <v>41927</v>
+      </c>
       <c r="I3" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="26"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
+      <c r="K3" s="26">
+        <v>44776</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>269</v>
+      </c>
       <c r="N3" s="19" t="s">
         <v>18</v>
       </c>
@@ -10119,25 +10471,39 @@
       <c r="B4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="C4" s="27">
+        <v>1697</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>297</v>
+      </c>
       <c r="F4" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H4" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H4" s="26">
+        <v>40882</v>
+      </c>
       <c r="I4" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
+      <c r="K4" s="26">
+        <v>44776</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>455</v>
+      </c>
       <c r="N4" s="19" t="s">
         <v>18</v>
       </c>
@@ -10149,24 +10515,36 @@
       <c r="B5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="C5" s="25">
+        <v>1700</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="F5" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H5" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H5" s="26">
+        <v>43661</v>
+      </c>
       <c r="I5" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K5" s="26"/>
-      <c r="L5" s="19"/>
+      <c r="K5" s="26">
+        <v>44777</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>457</v>
+      </c>
       <c r="M5" s="19"/>
       <c r="N5" s="19" t="s">
         <v>18</v>
@@ -10179,27 +10557,41 @@
       <c r="B6" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="C6" s="27">
+        <v>1739</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>353</v>
+      </c>
       <c r="F6" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H6" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H6" s="26">
+        <v>41797</v>
+      </c>
       <c r="I6" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J6" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K6" s="26"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
+      <c r="K6" s="26">
+        <v>44776</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>387</v>
+      </c>
       <c r="N6" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="28" customFormat="1">
@@ -10209,27 +10601,41 @@
       <c r="B7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="C7" s="25">
+        <v>1747</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>459</v>
+      </c>
       <c r="F7" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H7" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H7" s="26">
+        <v>41836</v>
+      </c>
       <c r="I7" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J7" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
+      <c r="K7" s="26">
+        <v>44776</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>402</v>
+      </c>
       <c r="N7" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="28" customFormat="1">
@@ -10239,27 +10645,39 @@
       <c r="B8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="C8" s="27">
+        <v>1777</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>461</v>
+      </c>
       <c r="F8" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H8" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H8" s="26">
+        <v>41623</v>
+      </c>
       <c r="I8" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="19"/>
+      <c r="K8" s="26">
+        <v>44781</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>462</v>
+      </c>
       <c r="M8" s="19"/>
       <c r="N8" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="28" customFormat="1">
@@ -10269,27 +10687,41 @@
       <c r="B9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="C9" s="25">
+        <v>1861</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="F9" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H9" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H9" s="26">
+        <v>41275</v>
+      </c>
       <c r="I9" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
+      <c r="K9" s="26">
+        <v>45154</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>265</v>
+      </c>
       <c r="N9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="28" customFormat="1">
@@ -10299,25 +10731,39 @@
       <c r="B10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="C10" s="27">
+        <v>1862</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="F10" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H10" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H10" s="26">
+        <v>41640</v>
+      </c>
       <c r="I10" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
+      <c r="K10" s="26">
+        <v>45154</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>265</v>
+      </c>
       <c r="N10" s="19" t="s">
         <v>19</v>
       </c>
@@ -10329,27 +10775,39 @@
       <c r="B11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="C11" s="25">
+        <v>1944</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>384</v>
+      </c>
       <c r="F11" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H11" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H11" s="26">
+        <v>40573</v>
+      </c>
       <c r="I11" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K11" s="26"/>
-      <c r="L11" s="19"/>
+      <c r="K11" s="26">
+        <v>45527</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>450</v>
+      </c>
       <c r="M11" s="19"/>
       <c r="N11" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="28" customFormat="1">
@@ -10359,27 +10817,39 @@
       <c r="B12" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="C12" s="27">
+        <v>1945</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>384</v>
+      </c>
       <c r="F12" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H12" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H12" s="26">
+        <v>41463</v>
+      </c>
       <c r="I12" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K12" s="26"/>
-      <c r="L12" s="19"/>
+      <c r="K12" s="26">
+        <v>45527</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>450</v>
+      </c>
       <c r="M12" s="19"/>
       <c r="N12" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="28" customFormat="1">
@@ -10389,27 +10859,39 @@
       <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="C13" s="25">
+        <v>1946</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>468</v>
+      </c>
       <c r="F13" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H13" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H13" s="26">
+        <v>41005</v>
+      </c>
       <c r="I13" s="27" t="s">
         <v>169</v>
       </c>
       <c r="J13" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K13" s="26"/>
-      <c r="L13" s="19"/>
+      <c r="K13" s="26">
+        <v>45528</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>469</v>
+      </c>
       <c r="M13" s="19"/>
       <c r="N13" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="28" customFormat="1">
@@ -10419,25 +10901,39 @@
       <c r="B14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="27">
+        <v>2010</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>470</v>
+      </c>
       <c r="F14" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H14" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H14" s="26">
+        <v>41582</v>
+      </c>
       <c r="I14" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J14" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K14" s="26"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
+      <c r="K14" s="26">
+        <v>45541</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>472</v>
+      </c>
       <c r="N14" s="19" t="s">
         <v>18</v>
       </c>
@@ -10449,27 +10945,39 @@
       <c r="B15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="C15" s="25">
+        <v>1727</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>120</v>
+      </c>
       <c r="F15" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H15" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H15" s="26">
+        <v>42005</v>
+      </c>
       <c r="I15" s="27" t="s">
         <v>169</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="19"/>
+      <c r="K15" s="26">
+        <v>44776</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>121</v>
+      </c>
       <c r="M15" s="19"/>
       <c r="N15" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="28" customFormat="1">
@@ -10479,24 +10987,36 @@
       <c r="B16" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="C16" s="27">
+        <v>1728</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>120</v>
+      </c>
       <c r="F16" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H16" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H16" s="26">
+        <v>41275</v>
+      </c>
       <c r="I16" s="27" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="J16" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="19"/>
+      <c r="K16" s="26">
+        <v>44776</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>121</v>
+      </c>
       <c r="M16" s="19"/>
       <c r="N16" s="19" t="s">
         <v>18</v>
@@ -10509,27 +11029,41 @@
       <c r="B17" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="25">
+        <v>1729</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>353</v>
+      </c>
       <c r="F17" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H17" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H17" s="26">
+        <v>40776</v>
+      </c>
       <c r="I17" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
+      <c r="K17" s="26">
+        <v>45507</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>387</v>
+      </c>
       <c r="N17" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="28" customFormat="1">
@@ -10539,14 +11073,20 @@
       <c r="B18" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="C18" s="27">
+        <v>1765</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>28</v>
+      </c>
       <c r="F18" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>229</v>
+        <v>452</v>
       </c>
       <c r="H18" s="26"/>
       <c r="I18" s="27" t="s">
@@ -10555,9 +11095,15 @@
       <c r="J18" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
+      <c r="K18" s="26">
+        <v>44781</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>96</v>
+      </c>
       <c r="N18" s="19" t="s">
         <v>18</v>
       </c>
@@ -10570,13 +11116,17 @@
         <v>24</v>
       </c>
       <c r="C19" s="25"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="D19" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>479</v>
+      </c>
       <c r="F19" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>229</v>
+        <v>452</v>
       </c>
       <c r="H19" s="26"/>
       <c r="I19" s="27" t="s">
@@ -10599,1094 +11149,38 @@
       <c r="B20" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="27">
+        <v>1768</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>272</v>
+      </c>
       <c r="F20" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H20" s="26"/>
+        <v>452</v>
+      </c>
+      <c r="H20" s="26">
+        <v>41491</v>
+      </c>
       <c r="I20" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J20" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K20" s="26"/>
-      <c r="L20" s="19"/>
+      <c r="K20" s="26">
+        <v>44781</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>481</v>
+      </c>
       <c r="M20" s="19"/>
       <c r="N20" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="28" customFormat="1">
-      <c r="A21" s="19">
-        <v>19</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H21" s="26"/>
-      <c r="I21" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K21" s="26"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" s="28" customFormat="1">
-      <c r="A22" s="19">
-        <v>20</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H22" s="26"/>
-      <c r="I22" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K22" s="26"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" s="28" customFormat="1">
-      <c r="A23" s="19">
-        <v>21</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K23" s="26"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" s="28" customFormat="1">
-      <c r="A24" s="19">
-        <v>22</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H24" s="26"/>
-      <c r="I24" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K24" s="26"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" s="28" customFormat="1">
-      <c r="A25" s="19">
-        <v>23</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H25" s="26"/>
-      <c r="I25" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K25" s="26"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="28" customFormat="1">
-      <c r="A26" s="19">
-        <v>24</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K26" s="26"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="28" customFormat="1">
-      <c r="A27" s="19">
-        <v>25</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H27" s="26"/>
-      <c r="I27" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K27" s="26"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="28" customFormat="1">
-      <c r="A28" s="19">
-        <v>26</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="27">
-        <v>1763</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H28" s="26"/>
-      <c r="I28" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K28" s="26"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="28" customFormat="1">
-      <c r="A29" s="19">
-        <v>27</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="25">
-        <v>1821</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H29" s="26"/>
-      <c r="I29" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K29" s="26"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="28" customFormat="1">
-      <c r="A30" s="19">
-        <v>28</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="27">
-        <v>1847</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H30" s="26"/>
-      <c r="I30" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K30" s="26"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="28" customFormat="1">
-      <c r="A31" s="19">
-        <v>29</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="25">
-        <v>1886</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H31" s="26"/>
-      <c r="I31" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K31" s="26"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" s="28" customFormat="1">
-      <c r="A32" s="19">
-        <v>30</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="27">
-        <v>1887</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H32" s="26"/>
-      <c r="I32" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K32" s="26"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="28" customFormat="1">
-      <c r="A33" s="19">
-        <v>31</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="25">
-        <v>1889</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H33" s="26"/>
-      <c r="I33" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K33" s="26"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="28" customFormat="1">
-      <c r="A34" s="19">
-        <v>32</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="27">
-        <v>1890</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H34" s="26"/>
-      <c r="I34" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K34" s="26"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="28" customFormat="1">
-      <c r="A35" s="19">
-        <v>33</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="25">
-        <v>1892</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H35" s="26"/>
-      <c r="I35" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K35" s="26"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="28" customFormat="1">
-      <c r="A36" s="19">
-        <v>34</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="27">
-        <v>1893</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H36" s="26"/>
-      <c r="I36" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K36" s="26"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" s="28" customFormat="1">
-      <c r="A37" s="19">
-        <v>35</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="25">
-        <v>1902</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H37" s="26"/>
-      <c r="I37" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K37" s="26"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="28" customFormat="1">
-      <c r="A38" s="19">
-        <v>36</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="27">
-        <v>1909</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H38" s="26"/>
-      <c r="I38" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K38" s="26"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" s="28" customFormat="1">
-      <c r="A39" s="19">
-        <v>37</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="25">
-        <v>1913</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H39" s="26"/>
-      <c r="I39" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K39" s="26"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" s="28" customFormat="1">
-      <c r="A40" s="19">
-        <v>38</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="27">
-        <v>1919</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H40" s="26"/>
-      <c r="I40" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K40" s="26"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" s="28" customFormat="1">
-      <c r="A41" s="19">
-        <v>39</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="25">
-        <v>1920</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H41" s="26"/>
-      <c r="I41" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K41" s="26"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" s="28" customFormat="1">
-      <c r="A42" s="19">
-        <v>40</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="27">
-        <v>1921</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H42" s="26"/>
-      <c r="I42" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K42" s="26"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" s="28" customFormat="1">
-      <c r="A43" s="19">
-        <v>41</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="25">
-        <v>1927</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H43" s="26"/>
-      <c r="I43" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K43" s="26"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="19">
-        <v>42</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="25">
-        <v>1928</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H44" s="26"/>
-      <c r="I44" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K44" s="26"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="19">
-        <v>43</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="25">
-        <v>1929</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H45" s="26"/>
-      <c r="I45" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K45" s="26"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="19">
-        <v>44</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="25">
-        <v>1947</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H46" s="26"/>
-      <c r="I46" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K46" s="26"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="19">
-        <v>45</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="25"/>
-      <c r="D47" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H47" s="26"/>
-      <c r="I47" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J47" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K47" s="26"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="19">
-        <v>46</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="25"/>
-      <c r="D48" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H48" s="26"/>
-      <c r="I48" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J48" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K48" s="26"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="19">
-        <v>47</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H49" s="26"/>
-      <c r="I49" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K49" s="26"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="19">
-        <v>48</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H50" s="26"/>
-      <c r="I50" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J50" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K50" s="26"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="19">
-        <v>49</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="25"/>
-      <c r="D51" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H51" s="26"/>
-      <c r="I51" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K51" s="26"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -11694,11 +11188,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="L1:L9 L11:L1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L10">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <conditionalFormatting sqref="L1:L1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -11706,8 +11198,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="20" customWidth="1"/>
@@ -11796,25 +11288,39 @@
       <c r="B3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+      <c r="C3" s="25">
+        <v>1645</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>546</v>
+      </c>
       <c r="F3" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H3" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H3" s="26">
+        <v>42003</v>
+      </c>
       <c r="I3" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="26"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
+      <c r="K3" s="26">
+        <v>44411</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>541</v>
+      </c>
       <c r="N3" s="19" t="s">
         <v>18</v>
       </c>
@@ -11826,25 +11332,39 @@
       <c r="B4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="C4" s="27">
+        <v>1648</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>28</v>
+      </c>
       <c r="F4" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H4" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H4" s="26">
+        <v>42328</v>
+      </c>
       <c r="I4" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
+      <c r="K4" s="26">
+        <v>44411</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>96</v>
+      </c>
       <c r="N4" s="19" t="s">
         <v>18</v>
       </c>
@@ -11856,25 +11376,39 @@
       <c r="B5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="C5" s="25">
+        <v>1641</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>549</v>
+      </c>
       <c r="F5" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H5" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H5" s="26">
+        <v>41030</v>
+      </c>
       <c r="I5" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K5" s="26"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
+      <c r="K5" s="26">
+        <v>44411</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>550</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>551</v>
+      </c>
       <c r="N5" s="19" t="s">
         <v>18</v>
       </c>
@@ -11886,25 +11420,39 @@
       <c r="B6" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="C6" s="27">
+        <v>1609</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>553</v>
+      </c>
       <c r="F6" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H6" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H6" s="26">
+        <v>41611</v>
+      </c>
       <c r="I6" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J6" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K6" s="26"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
+      <c r="K6" s="26">
+        <v>43315</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>555</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>556</v>
+      </c>
       <c r="N6" s="19" t="s">
         <v>18</v>
       </c>
@@ -11916,27 +11464,41 @@
       <c r="B7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="C7" s="25">
+        <v>1712</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>558</v>
+      </c>
       <c r="F7" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H7" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H7" s="26">
+        <v>40852</v>
+      </c>
       <c r="I7" s="27" t="s">
         <v>169</v>
       </c>
       <c r="J7" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
+      <c r="K7" s="26">
+        <v>44776</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>559</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>560</v>
+      </c>
       <c r="N7" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="28" customFormat="1">
@@ -11946,27 +11508,41 @@
       <c r="B8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="C8" s="27">
+        <v>1710</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>30</v>
+      </c>
       <c r="F8" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H8" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H8" s="26">
+        <v>42134</v>
+      </c>
       <c r="I8" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
+      <c r="K8" s="26">
+        <v>44777</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>148</v>
+      </c>
       <c r="N8" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="28" customFormat="1">
@@ -11976,25 +11552,39 @@
       <c r="B9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="C9" s="25">
+        <v>1949</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>563</v>
+      </c>
       <c r="F9" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H9" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H9" s="26">
+        <v>41497</v>
+      </c>
       <c r="I9" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
+      <c r="K9" s="26">
+        <v>45528</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>565</v>
+      </c>
       <c r="N9" s="19" t="s">
         <v>18</v>
       </c>
@@ -12006,27 +11596,41 @@
       <c r="B10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="C10" s="27">
+        <v>1858</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>567</v>
+      </c>
       <c r="F10" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H10" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H10" s="26">
+        <v>41776</v>
+      </c>
       <c r="I10" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
+      <c r="K10" s="26">
+        <v>44958</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>568</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>569</v>
+      </c>
       <c r="N10" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="28" customFormat="1">
@@ -12036,27 +11640,41 @@
       <c r="B11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="C11" s="25">
+        <v>1699</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>571</v>
+      </c>
       <c r="F11" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H11" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H11" s="26">
+        <v>43030</v>
+      </c>
       <c r="I11" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K11" s="26"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
+      <c r="K11" s="26">
+        <v>44776</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>573</v>
+      </c>
       <c r="N11" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="28" customFormat="1">
@@ -12066,16 +11684,24 @@
       <c r="B12" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="C12" s="27">
+        <v>1796</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>575</v>
+      </c>
       <c r="F12" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H12" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H12" s="26">
+        <v>41702</v>
+      </c>
       <c r="I12" s="27" t="s">
         <v>17</v>
       </c>
@@ -12083,8 +11709,12 @@
         <v>337</v>
       </c>
       <c r="K12" s="26"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
+      <c r="L12" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>577</v>
+      </c>
       <c r="N12" s="19" t="s">
         <v>18</v>
       </c>
@@ -12096,27 +11726,41 @@
       <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="C13" s="25">
+        <v>1654</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>579</v>
+      </c>
       <c r="F13" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H13" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H13" s="26">
+        <v>41846</v>
+      </c>
       <c r="I13" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J13" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K13" s="26"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
+      <c r="K13" s="26">
+        <v>44411</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>580</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>581</v>
+      </c>
       <c r="N13" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="28" customFormat="1">
@@ -12126,25 +11770,39 @@
       <c r="B14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="27">
+        <v>1603</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>582</v>
+      </c>
       <c r="F14" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H14" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H14" s="26">
+        <v>41902</v>
+      </c>
       <c r="I14" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J14" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K14" s="26"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
+      <c r="K14" s="26">
+        <v>43327</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>583</v>
+      </c>
       <c r="N14" s="19" t="s">
         <v>18</v>
       </c>
@@ -12156,25 +11814,39 @@
       <c r="B15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="C15" s="25">
+        <v>1950</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>132</v>
+      </c>
       <c r="F15" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H15" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H15" s="26">
+        <v>42646</v>
+      </c>
       <c r="I15" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
+      <c r="K15" s="26">
+        <v>45528</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>585</v>
+      </c>
       <c r="N15" s="19" t="s">
         <v>18</v>
       </c>
@@ -12186,25 +11858,39 @@
       <c r="B16" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="C16" s="27">
+        <v>1722</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>120</v>
+      </c>
       <c r="F16" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H16" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H16" s="26">
+        <v>40909</v>
+      </c>
       <c r="I16" s="27" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="J16" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
+      <c r="K16" s="26">
+        <v>44411</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>586</v>
+      </c>
       <c r="N16" s="19" t="s">
         <v>18</v>
       </c>
@@ -12216,25 +11902,39 @@
       <c r="B17" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="25">
+        <v>1656</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>587</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>588</v>
+      </c>
       <c r="F17" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H17" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H17" s="26">
+        <v>41811</v>
+      </c>
       <c r="I17" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
+      <c r="K17" s="26">
+        <v>44411</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>540</v>
+      </c>
       <c r="N17" s="19" t="s">
         <v>18</v>
       </c>
@@ -12247,13 +11947,17 @@
         <v>24</v>
       </c>
       <c r="C18" s="27"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="D18" s="17" t="s">
+        <v>590</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>490</v>
+      </c>
       <c r="F18" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>229</v>
+        <v>554</v>
       </c>
       <c r="H18" s="26"/>
       <c r="I18" s="27" t="s">
@@ -12276,25 +11980,39 @@
       <c r="B19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="C19" s="25">
+        <v>1908</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>379</v>
+      </c>
       <c r="F19" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H19" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H19" s="26">
+        <v>41833</v>
+      </c>
       <c r="I19" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K19" s="26"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
+      <c r="K19" s="26">
+        <v>45141</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>592</v>
+      </c>
       <c r="N19" s="19" t="s">
         <v>18</v>
       </c>
@@ -12306,25 +12024,39 @@
       <c r="B20" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="27">
+        <v>1948</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>490</v>
+      </c>
       <c r="F20" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H20" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H20" s="26">
+        <v>42658</v>
+      </c>
       <c r="I20" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J20" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K20" s="26"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
+      <c r="K20" s="26">
+        <v>45525</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>532</v>
+      </c>
       <c r="N20" s="19" t="s">
         <v>18</v>
       </c>
@@ -12336,27 +12068,41 @@
       <c r="B21" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="C21" s="25">
+        <v>1951</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>571</v>
+      </c>
       <c r="F21" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H21" s="26"/>
+        <v>554</v>
+      </c>
+      <c r="H21" s="26">
+        <v>42607</v>
+      </c>
       <c r="I21" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J21" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K21" s="26"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
+      <c r="K21" s="26">
+        <v>45141</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>573</v>
+      </c>
       <c r="N21" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="28" customFormat="1">
@@ -12366,14 +12112,20 @@
       <c r="B22" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="C22" s="27">
+        <v>1002</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>150</v>
+      </c>
       <c r="F22" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>229</v>
+        <v>554</v>
       </c>
       <c r="H22" s="26"/>
       <c r="I22" s="27" t="s">
@@ -12382,1018 +12134,14 @@
       <c r="J22" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K22" s="26"/>
+      <c r="K22" s="26">
+        <v>45528</v>
+      </c>
       <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
+      <c r="M22" s="19" t="s">
+        <v>595</v>
+      </c>
       <c r="N22" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" s="28" customFormat="1">
-      <c r="A23" s="19">
-        <v>21</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K23" s="26"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" s="28" customFormat="1">
-      <c r="A24" s="19">
-        <v>22</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H24" s="26"/>
-      <c r="I24" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K24" s="26"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" s="28" customFormat="1">
-      <c r="A25" s="19">
-        <v>23</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H25" s="26"/>
-      <c r="I25" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K25" s="26"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="28" customFormat="1">
-      <c r="A26" s="19">
-        <v>24</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K26" s="26"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="28" customFormat="1">
-      <c r="A27" s="19">
-        <v>25</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H27" s="26"/>
-      <c r="I27" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K27" s="26"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="28" customFormat="1">
-      <c r="A28" s="19">
-        <v>26</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="27">
-        <v>1763</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H28" s="26"/>
-      <c r="I28" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K28" s="26"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="28" customFormat="1">
-      <c r="A29" s="19">
-        <v>27</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="25">
-        <v>1821</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H29" s="26"/>
-      <c r="I29" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K29" s="26"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="28" customFormat="1">
-      <c r="A30" s="19">
-        <v>28</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="27">
-        <v>1847</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H30" s="26"/>
-      <c r="I30" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K30" s="26"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="28" customFormat="1">
-      <c r="A31" s="19">
-        <v>29</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="25">
-        <v>1886</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H31" s="26"/>
-      <c r="I31" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K31" s="26"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" s="28" customFormat="1">
-      <c r="A32" s="19">
-        <v>30</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="27">
-        <v>1887</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H32" s="26"/>
-      <c r="I32" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K32" s="26"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="28" customFormat="1">
-      <c r="A33" s="19">
-        <v>31</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="25">
-        <v>1889</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H33" s="26"/>
-      <c r="I33" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K33" s="26"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="28" customFormat="1">
-      <c r="A34" s="19">
-        <v>32</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="27">
-        <v>1890</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H34" s="26"/>
-      <c r="I34" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K34" s="26"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="28" customFormat="1">
-      <c r="A35" s="19">
-        <v>33</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="25">
-        <v>1892</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H35" s="26"/>
-      <c r="I35" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K35" s="26"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="28" customFormat="1">
-      <c r="A36" s="19">
-        <v>34</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="27">
-        <v>1893</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H36" s="26"/>
-      <c r="I36" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K36" s="26"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" s="28" customFormat="1">
-      <c r="A37" s="19">
-        <v>35</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="25">
-        <v>1902</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H37" s="26"/>
-      <c r="I37" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K37" s="26"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="28" customFormat="1">
-      <c r="A38" s="19">
-        <v>36</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="27">
-        <v>1909</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H38" s="26"/>
-      <c r="I38" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K38" s="26"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" s="28" customFormat="1">
-      <c r="A39" s="19">
-        <v>37</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="25">
-        <v>1913</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H39" s="26"/>
-      <c r="I39" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K39" s="26"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" s="28" customFormat="1">
-      <c r="A40" s="19">
-        <v>38</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="27">
-        <v>1919</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H40" s="26"/>
-      <c r="I40" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K40" s="26"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" s="28" customFormat="1">
-      <c r="A41" s="19">
-        <v>39</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="25">
-        <v>1920</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H41" s="26"/>
-      <c r="I41" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K41" s="26"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" s="28" customFormat="1">
-      <c r="A42" s="19">
-        <v>40</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="27">
-        <v>1921</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H42" s="26"/>
-      <c r="I42" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K42" s="26"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" s="28" customFormat="1">
-      <c r="A43" s="19">
-        <v>41</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="25">
-        <v>1927</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H43" s="26"/>
-      <c r="I43" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K43" s="26"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="19">
-        <v>42</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="25">
-        <v>1928</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H44" s="26"/>
-      <c r="I44" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K44" s="26"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="19">
-        <v>43</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="25">
-        <v>1929</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H45" s="26"/>
-      <c r="I45" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K45" s="26"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="19">
-        <v>44</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="25">
-        <v>1947</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H46" s="26"/>
-      <c r="I46" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K46" s="26"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="19">
-        <v>45</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="25"/>
-      <c r="D47" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H47" s="26"/>
-      <c r="I47" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J47" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K47" s="26"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="19">
-        <v>46</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="25"/>
-      <c r="D48" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H48" s="26"/>
-      <c r="I48" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J48" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K48" s="26"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="19">
-        <v>47</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H49" s="26"/>
-      <c r="I49" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K49" s="26"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="19">
-        <v>48</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H50" s="26"/>
-      <c r="I50" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J50" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K50" s="26"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="19">
-        <v>49</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="25"/>
-      <c r="D51" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H51" s="26"/>
-      <c r="I51" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K51" s="26"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -13413,8 +12161,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N51"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="20" customWidth="1"/>
@@ -13503,25 +12251,39 @@
       <c r="B3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+      <c r="C3" s="25">
+        <v>1576</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>342</v>
+      </c>
       <c r="F3" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H3" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H3" s="26">
+        <v>41036</v>
+      </c>
       <c r="I3" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J3" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K3" s="26"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
+      <c r="K3" s="26">
+        <v>43316</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>344</v>
+      </c>
       <c r="N3" s="19" t="s">
         <v>18</v>
       </c>
@@ -13533,25 +12295,39 @@
       <c r="B4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="C4" s="27">
+        <v>1574</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>272</v>
+      </c>
       <c r="F4" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H4" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H4" s="26">
+        <v>40765</v>
+      </c>
       <c r="I4" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J4" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
+      <c r="K4" s="26">
+        <v>43317</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>486</v>
+      </c>
       <c r="N4" s="19" t="s">
         <v>18</v>
       </c>
@@ -13563,25 +12339,39 @@
       <c r="B5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="C5" s="25">
+        <v>1626</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>28</v>
+      </c>
       <c r="F5" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H5" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H5" s="26">
+        <v>41974</v>
+      </c>
       <c r="I5" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J5" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K5" s="26"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
+      <c r="K5" s="26">
+        <v>44046</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>96</v>
+      </c>
       <c r="N5" s="19" t="s">
         <v>18</v>
       </c>
@@ -13593,25 +12383,39 @@
       <c r="B6" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="C6" s="27">
+        <v>1676</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>488</v>
+      </c>
       <c r="F6" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H6" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H6" s="26">
+        <v>40350</v>
+      </c>
       <c r="I6" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J6" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K6" s="26"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
+      <c r="K6" s="26">
+        <v>44411</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>531</v>
+      </c>
       <c r="N6" s="19" t="s">
         <v>18</v>
       </c>
@@ -13623,25 +12427,39 @@
       <c r="B7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="C7" s="25">
+        <v>1782</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>490</v>
+      </c>
       <c r="F7" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H7" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H7" s="26">
+        <v>41191</v>
+      </c>
       <c r="I7" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J7" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
+      <c r="K7" s="26">
+        <v>44781</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>519</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>532</v>
+      </c>
       <c r="N7" s="19" t="s">
         <v>19</v>
       </c>
@@ -13653,25 +12471,39 @@
       <c r="B8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="C8" s="27">
+        <v>1781</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>492</v>
+      </c>
       <c r="F8" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H8" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H8" s="26">
+        <v>40888</v>
+      </c>
       <c r="I8" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
+      <c r="K8" s="26">
+        <v>44781</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>533</v>
+      </c>
       <c r="N8" s="19" t="s">
         <v>19</v>
       </c>
@@ -13683,25 +12515,39 @@
       <c r="B9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="C9" s="25">
+        <v>1566</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>494</v>
+      </c>
       <c r="F9" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H9" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H9" s="26">
+        <v>42333</v>
+      </c>
       <c r="I9" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
+      <c r="K9" s="26">
+        <v>43316</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>534</v>
+      </c>
       <c r="N9" s="19" t="s">
         <v>18</v>
       </c>
@@ -13713,25 +12559,39 @@
       <c r="B10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="C10" s="27">
+        <v>1793</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>496</v>
+      </c>
       <c r="F10" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H10" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H10" s="26">
+        <v>40756</v>
+      </c>
       <c r="I10" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
+      <c r="K10" s="26">
+        <v>44929</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>535</v>
+      </c>
       <c r="N10" s="19" t="s">
         <v>19</v>
       </c>
@@ -13743,25 +12603,39 @@
       <c r="B11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="C11" s="25">
+        <v>1934</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="F11" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H11" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H11" s="26">
+        <v>42156</v>
+      </c>
       <c r="I11" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J11" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K11" s="26"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
+      <c r="K11" s="26">
+        <v>45525</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>536</v>
+      </c>
       <c r="N11" s="19" t="s">
         <v>18</v>
       </c>
@@ -13773,25 +12647,39 @@
       <c r="B12" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
+      <c r="C12" s="27">
+        <v>1792</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>240</v>
+      </c>
       <c r="F12" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H12" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H12" s="26">
+        <v>40413</v>
+      </c>
       <c r="I12" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J12" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K12" s="26"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
+      <c r="K12" s="26">
+        <v>45209</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>537</v>
+      </c>
       <c r="N12" s="19" t="s">
         <v>18</v>
       </c>
@@ -13803,25 +12691,39 @@
       <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
+      <c r="C13" s="25">
+        <v>1935</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>58</v>
+      </c>
       <c r="F13" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H13" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H13" s="26">
+        <v>40820</v>
+      </c>
       <c r="I13" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J13" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K13" s="26"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
+      <c r="K13" s="26">
+        <v>45525</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>207</v>
+      </c>
       <c r="N13" s="19" t="s">
         <v>19</v>
       </c>
@@ -13833,25 +12735,39 @@
       <c r="B14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="27">
+        <v>1790</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>492</v>
+      </c>
       <c r="F14" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H14" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H14" s="26">
+        <v>39992</v>
+      </c>
       <c r="I14" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J14" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K14" s="26"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
+      <c r="K14" s="26">
+        <v>45196</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>538</v>
+      </c>
       <c r="N14" s="19" t="s">
         <v>18</v>
       </c>
@@ -13863,25 +12779,39 @@
       <c r="B15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
+      <c r="C15" s="25">
+        <v>1791</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>501</v>
+      </c>
       <c r="F15" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H15" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H15" s="26">
+        <v>39942</v>
+      </c>
       <c r="I15" s="27" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
+      <c r="K15" s="26">
+        <v>45209</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>526</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>539</v>
+      </c>
       <c r="N15" s="19" t="s">
         <v>18</v>
       </c>
@@ -13893,25 +12823,39 @@
       <c r="B16" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
+      <c r="C16" s="27">
+        <v>1938</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>503</v>
+      </c>
       <c r="F16" s="19" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H16" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H16" s="26">
+        <v>40330</v>
+      </c>
       <c r="I16" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
+      <c r="K16" s="26">
+        <v>45526</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>181</v>
+      </c>
       <c r="N16" s="19" t="s">
         <v>18</v>
       </c>
@@ -13923,25 +12867,39 @@
       <c r="B17" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="25">
+        <v>1603</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>505</v>
+      </c>
       <c r="F17" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H17" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H17" s="26">
+        <v>41388</v>
+      </c>
       <c r="I17" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J17" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K17" s="26"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
+      <c r="K17" s="26">
+        <v>43327</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>540</v>
+      </c>
       <c r="N17" s="19" t="s">
         <v>18</v>
       </c>
@@ -13953,25 +12911,39 @@
       <c r="B18" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
+      <c r="C18" s="27">
+        <v>1630</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>493</v>
+      </c>
       <c r="F18" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H18" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H18" s="26">
+        <v>41315</v>
+      </c>
       <c r="I18" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J18" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K18" s="26"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
+      <c r="K18" s="26">
+        <v>44046</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>541</v>
+      </c>
       <c r="N18" s="19" t="s">
         <v>18</v>
       </c>
@@ -13983,25 +12955,39 @@
       <c r="B19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
+      <c r="C19" s="25">
+        <v>1632</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>267</v>
+      </c>
       <c r="F19" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H19" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H19" s="26">
+        <v>40453</v>
+      </c>
       <c r="I19" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J19" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K19" s="26"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
+      <c r="K19" s="26">
+        <v>44046</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>269</v>
+      </c>
       <c r="N19" s="19" t="s">
         <v>18</v>
       </c>
@@ -14013,25 +12999,39 @@
       <c r="B20" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="27">
+        <v>1637</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>509</v>
+      </c>
       <c r="F20" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H20" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H20" s="26">
+        <v>40399</v>
+      </c>
       <c r="I20" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J20" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K20" s="26"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
+      <c r="K20" s="26">
+        <v>44050</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>542</v>
+      </c>
       <c r="N20" s="19" t="s">
         <v>18</v>
       </c>
@@ -14043,25 +13043,39 @@
       <c r="B21" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="C21" s="25">
+        <v>1797</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>511</v>
+      </c>
       <c r="F21" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H21" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H21" s="26">
+        <v>41273</v>
+      </c>
       <c r="I21" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J21" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K21" s="26"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
+      <c r="K21" s="26">
+        <v>44051</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>294</v>
+      </c>
       <c r="N21" s="19" t="s">
         <v>18</v>
       </c>
@@ -14073,24 +13087,36 @@
       <c r="B22" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
+      <c r="C22" s="27">
+        <v>1631</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>513</v>
+      </c>
       <c r="F22" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H22" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H22" s="26">
+        <v>41377</v>
+      </c>
       <c r="I22" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J22" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K22" s="26"/>
-      <c r="L22" s="19"/>
+      <c r="K22" s="26">
+        <v>44046</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>322</v>
+      </c>
       <c r="M22" s="19"/>
       <c r="N22" s="19" t="s">
         <v>18</v>
@@ -14103,25 +13129,39 @@
       <c r="B23" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
+      <c r="C23" s="25">
+        <v>1936</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>278</v>
+      </c>
       <c r="F23" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H23" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H23" s="26">
+        <v>40616</v>
+      </c>
       <c r="I23" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J23" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K23" s="26"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
+      <c r="K23" s="26">
+        <v>45525</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>280</v>
+      </c>
       <c r="N23" s="19" t="s">
         <v>18</v>
       </c>
@@ -14133,25 +13173,39 @@
       <c r="B24" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="C24" s="27">
+        <v>1937</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>46</v>
+      </c>
       <c r="F24" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H24" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H24" s="26">
+        <v>41467</v>
+      </c>
       <c r="I24" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K24" s="26"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
+      <c r="K24" s="26">
+        <v>45525</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>543</v>
+      </c>
       <c r="N24" s="19" t="s">
         <v>19</v>
       </c>
@@ -14163,24 +13217,36 @@
       <c r="B25" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="C25" s="25">
+        <v>1969</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>228</v>
+      </c>
       <c r="F25" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H25" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H25" s="26">
+        <v>41562</v>
+      </c>
       <c r="I25" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J25" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K25" s="26"/>
-      <c r="L25" s="19"/>
+      <c r="K25" s="26">
+        <v>45532</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>188</v>
+      </c>
       <c r="M25" s="19"/>
       <c r="N25" s="19" t="s">
         <v>19</v>
@@ -14193,914 +13259,40 @@
       <c r="B26" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="C26" s="27">
+        <v>2009</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>517</v>
+      </c>
       <c r="F26" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H26" s="26"/>
+        <v>482</v>
+      </c>
+      <c r="H26" s="26">
+        <v>41840</v>
+      </c>
       <c r="I26" s="27" t="s">
         <v>17</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="K26" s="26"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
+      <c r="K26" s="26">
+        <v>45541</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>530</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>544</v>
+      </c>
       <c r="N26" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="28" customFormat="1">
-      <c r="A27" s="19">
-        <v>25</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H27" s="26"/>
-      <c r="I27" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K27" s="26"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="28" customFormat="1">
-      <c r="A28" s="19">
-        <v>26</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="27">
-        <v>1763</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H28" s="26"/>
-      <c r="I28" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K28" s="26"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="28" customFormat="1">
-      <c r="A29" s="19">
-        <v>27</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="25">
-        <v>1821</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H29" s="26"/>
-      <c r="I29" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K29" s="26"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="28" customFormat="1">
-      <c r="A30" s="19">
-        <v>28</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="27">
-        <v>1847</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H30" s="26"/>
-      <c r="I30" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K30" s="26"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="28" customFormat="1">
-      <c r="A31" s="19">
-        <v>29</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="25">
-        <v>1886</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H31" s="26"/>
-      <c r="I31" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K31" s="26"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" s="28" customFormat="1">
-      <c r="A32" s="19">
-        <v>30</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="27">
-        <v>1887</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H32" s="26"/>
-      <c r="I32" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K32" s="26"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="28" customFormat="1">
-      <c r="A33" s="19">
-        <v>31</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="25">
-        <v>1889</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H33" s="26"/>
-      <c r="I33" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K33" s="26"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="28" customFormat="1">
-      <c r="A34" s="19">
-        <v>32</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="27">
-        <v>1890</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H34" s="26"/>
-      <c r="I34" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K34" s="26"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="28" customFormat="1">
-      <c r="A35" s="19">
-        <v>33</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="25">
-        <v>1892</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H35" s="26"/>
-      <c r="I35" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K35" s="26"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="28" customFormat="1">
-      <c r="A36" s="19">
-        <v>34</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="27">
-        <v>1893</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H36" s="26"/>
-      <c r="I36" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K36" s="26"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" s="28" customFormat="1">
-      <c r="A37" s="19">
-        <v>35</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="25">
-        <v>1902</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H37" s="26"/>
-      <c r="I37" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K37" s="26"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="28" customFormat="1">
-      <c r="A38" s="19">
-        <v>36</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="27">
-        <v>1909</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H38" s="26"/>
-      <c r="I38" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K38" s="26"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" s="28" customFormat="1">
-      <c r="A39" s="19">
-        <v>37</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="25">
-        <v>1913</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H39" s="26"/>
-      <c r="I39" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K39" s="26"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" s="28" customFormat="1">
-      <c r="A40" s="19">
-        <v>38</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="27">
-        <v>1919</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H40" s="26"/>
-      <c r="I40" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K40" s="26"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" s="28" customFormat="1">
-      <c r="A41" s="19">
-        <v>39</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="25">
-        <v>1920</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H41" s="26"/>
-      <c r="I41" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K41" s="26"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" s="28" customFormat="1">
-      <c r="A42" s="19">
-        <v>40</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="27">
-        <v>1921</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H42" s="26"/>
-      <c r="I42" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K42" s="26"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" s="28" customFormat="1">
-      <c r="A43" s="19">
-        <v>41</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="25">
-        <v>1927</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H43" s="26"/>
-      <c r="I43" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K43" s="26"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="19">
-        <v>42</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="25">
-        <v>1928</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H44" s="26"/>
-      <c r="I44" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K44" s="26"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="19">
-        <v>43</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="25">
-        <v>1929</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="E45" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H45" s="26"/>
-      <c r="I45" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K45" s="26"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="19">
-        <v>44</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="25">
-        <v>1947</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H46" s="26"/>
-      <c r="I46" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K46" s="26"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="19">
-        <v>45</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="25"/>
-      <c r="D47" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>333</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H47" s="26"/>
-      <c r="I47" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J47" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K47" s="26"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="19">
-        <v>46</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="25"/>
-      <c r="D48" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>334</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H48" s="26"/>
-      <c r="I48" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J48" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K48" s="26"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="19">
-        <v>47</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="E49" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H49" s="26"/>
-      <c r="I49" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K49" s="26"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="19">
-        <v>48</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H50" s="26"/>
-      <c r="I50" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="J50" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K50" s="26"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="19">
-        <v>49</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="25"/>
-      <c r="D51" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="E51" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="H51" s="26"/>
-      <c r="I51" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="K51" s="26"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -15120,7 +13312,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -15134,8 +13326,8 @@
         <v>21</v>
       </c>
       <c r="B2" s="3">
-        <f>COUNTIF(ECE!$F:$F,"Female")</f>
-        <v>16</v>
+        <f>COUNTIF(ECE!$F$2:$F$37,"Female")+COUNTIF(KG!$F$2:$F$43,"Female")+COUNTIF('Class-1'!$F$2:$F$51,"Female")+COUNTIF('Class-2'!$F$2:$F$48,"Female")+COUNTIF('Class-3'!$F$2:$F$20,"Female")+COUNTIF('Class-4'!$F$2:$F$22,"Female")+COUNTIF('Class-5'!$F$2:$F$26,"Female")</f>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21">
@@ -15143,8 +13335,8 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(ECE!$F:$F,"Male")</f>
-        <v>19</v>
+        <f>COUNTIF(ECE!$F$2:$F$37,"Male")+COUNTIF(KG!$F$2:$F$43,"Male")+COUNTIF('Class-1'!$F$2:$F$51,"Male")+COUNTIF('Class-2'!$F$2:$F$48,"Male")+COUNTIF('Class-3'!$F$2:$F$20,"Male")+COUNTIF('Class-4'!$F$2:$F$22,"Male")+COUNTIF('Class-5'!$F$2:$F$26,"Male")</f>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21">
@@ -15153,7 +13345,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2+B3</f>
-        <v>35</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/Shafi Goth/GBPS Shafi Goth.xlsx
+++ b/Shafi Goth/GBPS Shafi Goth.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Shafi Goth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFF59971-264C-44F2-BA2F-0776116A57D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280739CB-B06C-49E9-8EE1-A80F3190D0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="621">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -1895,9 +1895,6 @@
   </si>
   <si>
     <t>0315-2887792</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
   <si>
     <t>0345-3355830</t>
@@ -2177,6 +2174,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2195,18 +2204,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2846,22 +2843,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="32"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="40"/>
     </row>
     <row r="2" spans="1:14" s="2" customFormat="1">
       <c r="A2" s="8" t="s">
@@ -2907,47 +2904,47 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="44" customFormat="1">
-      <c r="A3" s="38">
+    <row r="3" spans="1:14" s="38" customFormat="1">
+      <c r="A3" s="32">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="39">
+      <c r="B3" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="33">
         <v>1986</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="38" t="s">
+      <c r="F3" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="35">
         <v>43466</v>
       </c>
-      <c r="I3" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="K3" s="41">
+      <c r="I3" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="K3" s="35">
         <v>45537</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="L3" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="M3" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="N3" s="43" t="s">
+      <c r="N3" s="37" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4420,22 +4417,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="21" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:14" s="24" customFormat="1">
       <c r="A2" s="16" t="s">
@@ -4827,7 +4824,7 @@
         <v>106</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N10" s="19" t="s">
         <v>19</v>
@@ -4871,7 +4868,7 @@
         <v>106</v>
       </c>
       <c r="M11" s="19" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N11" s="19" t="s">
         <v>19</v>
@@ -6292,22 +6289,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="21" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:14" s="24" customFormat="1">
       <c r="A2" s="16" t="s">
@@ -7476,7 +7473,7 @@
         <v>44781</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>278</v>
@@ -8558,22 +8555,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="21" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:14" s="24" customFormat="1">
       <c r="A2" s="16" t="s">
@@ -10670,9 +10667,7 @@
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="45" t="s">
-        <v>616</v>
-      </c>
+      <c r="A50" s="39"/>
       <c r="G50"/>
     </row>
     <row r="51" spans="1:14">
@@ -10722,22 +10717,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="21" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:14" s="24" customFormat="1">
       <c r="A2" s="16" t="s">
@@ -10909,7 +10904,7 @@
         <v>448</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="N5" s="19" t="s">
         <v>18</v>
@@ -11041,7 +11036,7 @@
         <v>453</v>
       </c>
       <c r="M8" s="19" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="N8" s="19" t="s">
         <v>18</v>
@@ -11551,7 +11546,7 @@
         <v>472</v>
       </c>
       <c r="M20" s="19" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="N20" s="19" t="s">
         <v>18</v>
@@ -11593,22 +11588,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="21" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:14" s="24" customFormat="1">
       <c r="A2" s="16" t="s">
@@ -11780,7 +11775,7 @@
         <v>540</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="N5" s="19" t="s">
         <v>18</v>
@@ -12558,22 +12553,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="21" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="43"/>
     </row>
     <row r="2" spans="1:14" s="24" customFormat="1">
       <c r="A2" s="16" t="s">

--- a/Shafi Goth/GBPS Shafi Goth.xlsx
+++ b/Shafi Goth/GBPS Shafi Goth.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Shafi Goth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280739CB-B06C-49E9-8EE1-A80F3190D0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5FD09A-01B8-4894-9E08-BD91BCE29EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE" sheetId="1" r:id="rId1"/>
@@ -13698,8 +13698,8 @@
         <v>21</v>
       </c>
       <c r="B2" s="3">
-        <f>COUNTIF(ECE!$F$2:$F$35,"Female")+COUNTIF(KG!$F$2:$F$43,"Female")+COUNTIF('Class-1'!$F$2:$F$51,"Female")+COUNTIF('Class-2'!$F$2:$F$48,"Female")+COUNTIF('Class-3'!$F$2:$F$20,"Female")+COUNTIF('Class-4'!$F$2:$F$22,"Female")+COUNTIF('Class-5'!$F$2:$F$26,"Female")</f>
-        <v>98</v>
+        <f>COUNTIF(ECE!$F$2:$F$38,"Female")+COUNTIF(KG!$F$2:$F$43,"Female")+COUNTIF('Class-1'!$F$2:$F$52,"Female")+COUNTIF('Class-2'!$F$2:$F$49,"Female")+COUNTIF('Class-3'!$F$2:$F$20,"Female")+COUNTIF('Class-4'!$F$2:$F$22,"Female")+COUNTIF('Class-5'!$F$2:$F$26,"Female")</f>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21">
@@ -13707,7 +13707,7 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF(ECE!$F$2:$F$35,"Male")+COUNTIF(KG!$F$2:$F$43,"Male")+COUNTIF('Class-1'!$F$2:$F$51,"Male")+COUNTIF('Class-2'!$F$2:$F$48,"Male")+COUNTIF('Class-3'!$F$2:$F$20,"Male")+COUNTIF('Class-4'!$F$2:$F$22,"Male")+COUNTIF('Class-5'!$F$2:$F$26,"Male")</f>
+        <f>COUNTIF(ECE!$F$2:$F$38,"Male")+COUNTIF(KG!$F$2:$F$43,"Male")+COUNTIF('Class-1'!$F$2:$F$52,"Male")+COUNTIF('Class-2'!$F$2:$F$49,"Male")+COUNTIF('Class-3'!$F$2:$F$20,"Male")+COUNTIF('Class-4'!$F$2:$F$22,"Male")+COUNTIF('Class-5'!$F$2:$F$26,"Male")</f>
         <v>133</v>
       </c>
     </row>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="B4" s="3">
         <f>B2+B3</f>
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
